--- a/output/pdf_financials_xlsx/BTB.UN.xlsx
+++ b/output/pdf_financials_xlsx/BTB.UN.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>23.893</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>25.547</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">

--- a/output/pdf_financials_xlsx/BTB.UN.xlsx
+++ b/output/pdf_financials_xlsx/BTB.UN.xlsx
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>5.981</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>6.955</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>10.37</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>10.97</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>11.748</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>11.558</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>12.209</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
@@ -1204,22 +1204,22 @@
         <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-13.221</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-21.529</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-19.031</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-23.151</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-21.336</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-18.678</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>-0</v>
@@ -2220,22 +2220,22 @@
         <v>7.45</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>17.967</v>
+        <v>31.188</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.349</v>
+        <v>39.878</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12.883</v>
+        <v>31.914</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8.669</v>
+        <v>31.82</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>22.085</v>
+        <v>43.421</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>28.171</v>
+        <v>46.849</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>41.337</v>
@@ -2285,25 +2285,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
@@ -2350,25 +2350,25 @@
         <v>7.45</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.967</v>
+        <v>31.285</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.349</v>
+        <v>40.004</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>12.883</v>
+        <v>32.079</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.669</v>
+        <v>31.978</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>22.085</v>
+        <v>43.591</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>28.171</v>
+        <v>47.003</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>41.337</v>
+        <v>41.427</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>36.598</v>
+        <v>36.697</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>38.742</v>
+        <v>38.814</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -6691,37 +6691,37 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q100" s="3" t="n">
         <v>0</v>
@@ -30298,7 +30298,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -33096,7 +33100,11 @@
           <t>Comprehensive income - - 38,154 38,154 Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -34486,7 +34494,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36728,7 +36740,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -38216,7 +38232,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -39442,7 +39462,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -41064,7 +41088,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -49952,7 +49980,11 @@
           <t>Other operating costs</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -50216,7 +50248,11 @@
           <t>Net financing costs 17</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -51792,7 +51828,11 @@
           <t>Net financing costs 18</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
